--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,137 +424,152 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código Local</t>
+          <t>cui</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>cod_local</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Nombre de la I.E.</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Cuenta con Plan o Manual de Mantenimiento. SI/NO.</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Alcance del Plan o Manual (Mantenimiento recurrente, Mantenimiento preventivo, Mantenimienro correctivo)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento recurrente (ejecutado o proyectado) 2025</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento recurrente (ejecutado o proyectado) 2026</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento recurrente (ejecutado o proyectado) 2027</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento recurrente (ejecutado o proyectado) 2028</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento preventido (ejecutado o proyectado) 2025</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento preventido (ejecutado o proyectado) 2026</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento preventido (ejecutado o proyectado) 2027</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento preventido (ejecutado o proyectado) 2028</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento correctivo (ejecutado o proyectado) 2025</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento correctivo (ejecutado o proyectado) 2026</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento correctivo (ejecutado o proyectado) 2027</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Monto anual de mantenimiento correctivo (ejecutado o proyectado) 2028</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>- ALCANCE: Activos intervenidos (equipamiento educativo, mobiliario, instalaciones sanitarias, instalaciones eléctricas y mecánicas, tecnologías de la información y comunicaciones, sistemas de detección y alarmas, coberturas, acabados y exteriores).</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Avance (%)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Año de la entrega del PEIP</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Fecha de inicio del mantenimiento (o estimada)</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Fecha de culminación de mantenimiento (o estimada)</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Comentarios (- Otras variables que se consideren pertinentes para el seguimiento del avance en el cierre de brechas.)</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>centro_poblado</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ubigeo</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>ugel</t>
         </is>
       </c>
     </row>
@@ -564,75 +579,110 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2465303</t>
+          <t>2455491</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>311224</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>I.E. JORGE BASADRE GROHMANN</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>245014.47</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>245014.47</v>
       </c>
       <c r="I2" t="n">
+        <v>245014.47</v>
+      </c>
+      <c r="J2" t="n">
         <v>61253.61750000001</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>344058.55</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>344058.55</v>
       </c>
       <c r="M2" t="n">
+        <v>344058.55</v>
+      </c>
+      <c r="N2" t="n">
         <v>172029.275</v>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>2024</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>11/06/2025</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>150117</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -640,75 +690,110 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2475493</t>
+          <t>2465303</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>288054</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>I.E. NUESTRA SEÑORA DE LA VISITACION</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>365311.43</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>365311.43</v>
       </c>
       <c r="I3" t="n">
+        <v>365311.43</v>
+      </c>
+      <c r="J3" t="n">
         <v>91327.8575</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>469471.54</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>469471.54</v>
       </c>
       <c r="M3" t="n">
+        <v>469471.54</v>
+      </c>
+      <c r="N3" t="n">
         <v>234735.77</v>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>2024</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>11/06/2025</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>LIMA CERCADO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -716,75 +801,110 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2488285</t>
+          <t>2475493</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>304860</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>I.E. JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>405598.37</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>405598.37</v>
       </c>
       <c r="I4" t="n">
+        <v>405598.37</v>
+      </c>
+      <c r="J4" t="n">
         <v>101399.5925</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>511471.81</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>511471.81</v>
       </c>
       <c r="M4" t="n">
+        <v>511471.81</v>
+      </c>
+      <c r="N4" t="n">
         <v>255735.905</v>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>2024</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>11/06/2025</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>EL AGUSTINO</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EL AGUSTINO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>150111</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -797,70 +917,105 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>301913</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>I.E. SAN FELIPE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>438373.19</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>438373.19</v>
       </c>
       <c r="I5" t="n">
+        <v>438373.19</v>
+      </c>
+      <c r="J5" t="n">
         <v>109593.2975</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>634264.53</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>634264.53</v>
       </c>
       <c r="M5" t="n">
+        <v>634264.53</v>
+      </c>
+      <c r="N5" t="n">
         <v>317132.265</v>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>2024</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>11/06/2025</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>150110</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -873,70 +1028,105 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>291792</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>IE 1268 Gustavo Mohme</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>443448.39</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>443448.39</v>
       </c>
       <c r="I6" t="n">
+        <v>443448.39</v>
+      </c>
+      <c r="J6" t="n">
         <v>110862.0975</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>516568.69</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>516568.69</v>
       </c>
       <c r="M6" t="n">
+        <v>516568.69</v>
+      </c>
+      <c r="N6" t="n">
         <v>258284.345</v>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>2025</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -949,70 +1139,105 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>292490</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>IE 1209 Mscal. Toribio Luzuriaga</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>386946.03</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>386946.03</v>
       </c>
       <c r="I7" t="n">
+        <v>386946.03</v>
+      </c>
+      <c r="J7" t="n">
         <v>96736.50750000001</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>620446.98</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>620446.98</v>
       </c>
       <c r="M7" t="n">
+        <v>620446.98</v>
+      </c>
+      <c r="N7" t="n">
         <v>310223.49</v>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>2025</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1025,70 +1250,105 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>292126</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>IE Manuel Gonzales Prada</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
-        <v>925947.16</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>925947.16</v>
       </c>
       <c r="I8" t="n">
+        <v>925947.16</v>
+      </c>
+      <c r="J8" t="n">
         <v>231486.79</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>1453676.9</v>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>1453676.9</v>
       </c>
       <c r="M8" t="n">
+        <v>1453676.9</v>
+      </c>
+      <c r="N8" t="n">
         <v>726838.45</v>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>2025</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1101,70 +1361,105 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>292254</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>IE 046 Victor Raul Haya de la T</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>527451.5</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>527451.5</v>
       </c>
       <c r="I9" t="n">
+        <v>527451.5</v>
+      </c>
+      <c r="J9" t="n">
         <v>131862.875</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>929711.5</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>929711.5</v>
       </c>
       <c r="M9" t="n">
+        <v>929711.5</v>
+      </c>
+      <c r="N9" t="n">
         <v>464855.75</v>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>2025</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1177,70 +1472,105 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>313591</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>IE 1267</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
-        <v>551198.48</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>551198.48</v>
       </c>
       <c r="I10" t="n">
+        <v>551198.48</v>
+      </c>
+      <c r="J10" t="n">
         <v>137799.62</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>683162.4</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>683162.4</v>
       </c>
       <c r="M10" t="n">
+        <v>683162.4</v>
+      </c>
+      <c r="N10" t="n">
         <v>341581.2</v>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>2025</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>150118</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1253,70 +1583,105 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>311083</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>IE Peru Canada</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>486713.03</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>486713.03</v>
       </c>
       <c r="I11" t="n">
+        <v>486713.03</v>
+      </c>
+      <c r="J11" t="n">
         <v>121678.2575</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>561673.29</v>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>561673.29</v>
       </c>
       <c r="M11" t="n">
+        <v>561673.29</v>
+      </c>
+      <c r="N11" t="n">
         <v>280836.645</v>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>2025</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>150117</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1329,70 +1694,105 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>292598</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>IE 1255 Walter Peñaloza</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
-        <v>626924.48</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>626924.48</v>
       </c>
       <c r="I12" t="n">
+        <v>626924.48</v>
+      </c>
+      <c r="J12" t="n">
         <v>156731.12</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>762108.89</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>762108.89</v>
       </c>
       <c r="M12" t="n">
+        <v>762108.89</v>
+      </c>
+      <c r="N12" t="n">
         <v>381054.445</v>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>2025</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1405,70 +1805,105 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>292268</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>IE 034</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>181556.8</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>181556.8</v>
       </c>
       <c r="I13" t="n">
+        <v>181556.8</v>
+      </c>
+      <c r="J13" t="n">
         <v>45389.2</v>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>189278.1</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>189278.1</v>
       </c>
       <c r="M13" t="n">
+        <v>189278.1</v>
+      </c>
+      <c r="N13" t="n">
         <v>94639.05</v>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>2025</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>10/01/2026</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1481,70 +1916,105 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>307458</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>IE 1235 UNION LATINOAMERICANA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>483836.3</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>483836.3</v>
       </c>
       <c r="I14" t="n">
+        <v>483836.3</v>
+      </c>
+      <c r="J14" t="n">
         <v>120959.075</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>721457.8199999999</v>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>721457.8199999999</v>
       </c>
       <c r="M14" t="n">
+        <v>721457.8199999999</v>
+      </c>
+      <c r="N14" t="n">
         <v>360728.91</v>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>2024</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>LA MOLINA</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>LA MOLINA</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1557,70 +2027,105 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>298816</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>IE 6094 SANTA ROSA</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>448674.75</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>448674.75</v>
       </c>
       <c r="I15" t="n">
+        <v>448674.75</v>
+      </c>
+      <c r="J15" t="n">
         <v>112168.6875</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>576278.51</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>576278.51</v>
       </c>
       <c r="M15" t="n">
+        <v>576278.51</v>
+      </c>
+      <c r="N15" t="n">
         <v>288139.255</v>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>2024</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>150108</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1633,70 +2138,105 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>332165</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>IE 0083 SAN JUAN MACIAS</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
-        <v>472631.57</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>472631.57</v>
       </c>
       <c r="I16" t="n">
+        <v>472631.57</v>
+      </c>
+      <c r="J16" t="n">
         <v>118157.8925</v>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>492731.78</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>492731.78</v>
       </c>
       <c r="M16" t="n">
+        <v>492731.78</v>
+      </c>
+      <c r="N16" t="n">
         <v>246365.89</v>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>0</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>2024</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>150134</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1709,70 +2249,105 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>338855</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>IE 1221 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>369766.7</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>369766.7</v>
       </c>
       <c r="I17" t="n">
+        <v>369766.7</v>
+      </c>
+      <c r="J17" t="n">
         <v>92441.675</v>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>439753.44</v>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>439753.44</v>
       </c>
       <c r="M17" t="n">
+        <v>439753.44</v>
+      </c>
+      <c r="N17" t="n">
         <v>219876.72</v>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>2024</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>SANTA ANITA</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>SANTA ANITA</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1785,70 +2360,105 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>329889</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>IE 7207 MARISCAL RAMÓN CASTILLA</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>467638.29</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>467638.29</v>
       </c>
       <c r="I18" t="n">
+        <v>467638.29</v>
+      </c>
+      <c r="J18" t="n">
         <v>116909.5725</v>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>650309.74</v>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>650309.74</v>
       </c>
       <c r="M18" t="n">
+        <v>650309.74</v>
+      </c>
+      <c r="N18" t="n">
         <v>325154.87</v>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>2024</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>150133</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1861,70 +2471,105 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>340231</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>IE 7086 LOS PRECURSORES</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>523736.69</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>523736.69</v>
       </c>
       <c r="I19" t="n">
+        <v>523736.69</v>
+      </c>
+      <c r="J19" t="n">
         <v>130934.1725</v>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>654532.71</v>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>654532.71</v>
       </c>
       <c r="M19" t="n">
+        <v>654532.71</v>
+      </c>
+      <c r="N19" t="n">
         <v>327266.355</v>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>2024</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>LOS PRECURSORES</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>150140</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1937,70 +2582,105 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>340189</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>IE 6082 LOS PROCERES</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
-        <v>512259.31</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>512259.31</v>
       </c>
       <c r="I20" t="n">
+        <v>512259.31</v>
+      </c>
+      <c r="J20" t="n">
         <v>128064.8275</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>642567.21</v>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>642567.21</v>
       </c>
       <c r="M20" t="n">
+        <v>642567.21</v>
+      </c>
+      <c r="N20" t="n">
         <v>321283.605</v>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>2024</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>150140</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2013,70 +2693,105 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>329974</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>IE JAVIER HERAUD</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>669200.89</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>669200.89</v>
       </c>
       <c r="I21" t="n">
+        <v>669200.89</v>
+      </c>
+      <c r="J21" t="n">
         <v>167300.2225</v>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>1131750.45</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>1131750.45</v>
       </c>
       <c r="M21" t="n">
+        <v>1131750.45</v>
+      </c>
+      <c r="N21" t="n">
         <v>565875.225</v>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>0</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>2024</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>150133</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2089,70 +2804,105 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>320600</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>IE 2099 ROSA MERINO</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
-        <v>409693.48</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>409693.48</v>
       </c>
       <c r="I22" t="n">
+        <v>409693.48</v>
+      </c>
+      <c r="J22" t="n">
         <v>102423.37</v>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>427117.04</v>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>427117.04</v>
       </c>
       <c r="M22" t="n">
+        <v>427117.04</v>
+      </c>
+      <c r="N22" t="n">
         <v>213558.52</v>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>0</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>2024</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>RIMAC</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>RIMAC</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>150128</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2165,70 +2915,105 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>287988</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>IE 101- 1166 LIBERTADOR SIMÓN BOLIVAR</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
-        <v>353857.06</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>353857.06</v>
       </c>
       <c r="I23" t="n">
+        <v>353857.06</v>
+      </c>
+      <c r="J23" t="n">
         <v>88464.265</v>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>423167.19</v>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>423167.19</v>
       </c>
       <c r="M23" t="n">
+        <v>423167.19</v>
+      </c>
+      <c r="N23" t="n">
         <v>211583.595</v>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>0</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>2024</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>LIMA CERCADO</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,70 +3026,105 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>308783</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>IE 1124 JOSE MARTÍ</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>337397.07</v>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>337397.07</v>
       </c>
       <c r="I24" t="n">
+        <v>337397.07</v>
+      </c>
+      <c r="J24" t="n">
         <v>84349.2675</v>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>406007.18</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>406007.18</v>
       </c>
       <c r="M24" t="n">
+        <v>406007.18</v>
+      </c>
+      <c r="N24" t="n">
         <v>203003.59</v>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>NINGUNO</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>0</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>2024</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>No se cuenta con presupuesto asignado a la fecha</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>LIMA CERCADO</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>150101</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE24"/>
+  <dimension ref="A1:AF24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,11 @@
       <c r="AE1" t="inlineStr">
         <is>
           <t>ugel</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
@@ -683,6 +688,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -794,6 +804,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -905,6 +920,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1016,6 +1036,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1127,6 +1152,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1238,6 +1268,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1349,6 +1384,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2126,6 +2196,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2348,6 +2428,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2459,6 +2544,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2570,6 +2660,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2681,6 +2776,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2903,6 +3008,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3014,6 +3124,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3125,6 +3240,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF24"/>
+  <dimension ref="A1:AH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,6 +573,16 @@
         </is>
       </c>
       <c r="AF1" t="inlineStr">
+        <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -690,6 +700,16 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -806,6 +826,16 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>0035 NUESTRA SEÑORA DE LA VISITACION/0035 NUESTRA SEÑORA DE LA VISITACION/0035 NUESTRA SEÑORA DE LA VISITACION</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -922,6 +952,16 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1038,6 +1078,16 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>SAN FELIPE/SAN FELIPE</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1154,6 +1204,16 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>1268 GUSTAVO MOHME LLONA/1268 GUSTAVO MOHME LLONA</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1270,6 +1330,16 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>1209 MARISCAL TORIBIO DE LUZURIAGA/1209 MARISCAL TORIBIO DE LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1386,6 +1456,16 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALEZ PRADA</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1502,6 +1582,16 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>VICTOR RAUL HAYA DE LA TORRE/046 VICTOR RAUL HAYA DE LA TORRE</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1618,6 +1708,16 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>1267/1267/1267</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1734,6 +1834,16 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>3080 PERU - CANADA/3080 PERU - CANADA</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1850,6 +1960,16 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>1255 WALTER PEÑALOZA RAMELLA/1255 WALTER PEÑALOZA RAMELLA</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1966,6 +2086,16 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>0034 PERUANO FINLANDES</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2082,6 +2212,16 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2198,6 +2338,16 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>6094 SANTA ROSA/6094 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2314,6 +2464,16 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>0083 SAN JUAN MACIAS/0083 SAN JUAN MACIAS</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2430,6 +2590,16 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2546,6 +2716,16 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
+          <t>7207 MARISCAL RAMON CASTILLA/7207 MARISCAL RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2662,6 +2842,16 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>7086 LOS PRECURSORES/7086 LOS PRECURSORES/7086 LOS PRECURSORES</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2778,6 +2968,16 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
+          <t>6082 LOS PROCERES/6082 LOS PROCERES</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2894,6 +3094,16 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
+          <t>JAVIER HERAUD/JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3010,6 +3220,16 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
+          <t>2099 PATRICIA ROSA MERINO/2099 PATRICIA ROSA MERINO</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3126,6 +3346,16 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
+          <t>101 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3242,6 +3472,16 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
+          <t>1124 JOSE MARTI/1124 JOSE MARTI</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -434,107 +434,107 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Nombre de la I.E.</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Cuenta con Plan o Manual de Mantenimiento. SI/NO.</t>
+          <t>cuenta_con_plan_o_manual_de_mantenimiento_si_no</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Alcance del Plan o Manual (Mantenimiento recurrente, Mantenimiento preventivo, Mantenimienro correctivo)</t>
+          <t>alcance_del_plan_o_manual_mantenimiento_recurrente_mantenimi</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento recurrente (ejecutado o proyectado) 2025</t>
+          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento recurrente (ejecutado o proyectado) 2026</t>
+          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta_2</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento recurrente (ejecutado o proyectado) 2027</t>
+          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta_3</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento recurrente (ejecutado o proyectado) 2028</t>
+          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta_4</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento preventido (ejecutado o proyectado) 2025</t>
+          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento preventido (ejecutado o proyectado) 2026</t>
+          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta_2</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento preventido (ejecutado o proyectado) 2027</t>
+          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta_3</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento preventido (ejecutado o proyectado) 2028</t>
+          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta_4</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento correctivo (ejecutado o proyectado) 2025</t>
+          <t>monto_anual_de_mantenimiento_correctivo_ejecutado_o_proyecta</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento correctivo (ejecutado o proyectado) 2026</t>
+          <t>monto_anual_de_mantenimiento_correctivo_ejecutado_o_proyecta_2</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento correctivo (ejecutado o proyectado) 2027</t>
+          <t>monto_anual_de_mantenimiento_correctivo_ejecutado_o_proyecta_3</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Monto anual de mantenimiento correctivo (ejecutado o proyectado) 2028</t>
+          <t>monto_anual_de_mantenimiento_correctivo_ejecutado_o_proyecta_4</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>- ALCANCE: Activos intervenidos (equipamiento educativo, mobiliario, instalaciones sanitarias, instalaciones eléctricas y mecánicas, tecnologías de la información y comunicaciones, sistemas de detección y alarmas, coberturas, acabados y exteriores).</t>
+          <t>alcance_activos_intervenidos_equipamiento_educativo_mobiliar</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Avance (%)</t>
+          <t>avance</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Año de la entrega del PEIP</t>
+          <t>ano_de_la_entrega_del_peip</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Fecha de inicio del mantenimiento (o estimada)</t>
+          <t>fecha_de_inicio_del_mantenimiento_o_estimada</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Fecha de culminación de mantenimiento (o estimada)</t>
+          <t>fecha_de_culminacion_de_mantenimiento_o_estimada</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Comentarios (- Otras variables que se consideren pertinentes para el seguimiento del avance en el cierre de brechas.)</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_peip_mantenimiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH24"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,140 +449,100 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta</t>
+          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta_2</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta_2</t>
+          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta_4</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta_3</t>
+          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta_2</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_recurrente_ejecutado_o_proyecta_4</t>
+          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta_4</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta</t>
+          <t>alcance_activos_intervenidos_equipamiento_educativo_mobiliar</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta_2</t>
+          <t>avance</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta_3</t>
+          <t>ano_de_la_entrega_del_peip</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_preventido_ejecutado_o_proyecta_4</t>
+          <t>fecha_de_inicio_del_mantenimiento_o_estimada</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_correctivo_ejecutado_o_proyecta</t>
+          <t>fecha_de_culminacion_de_mantenimiento_o_estimada</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_correctivo_ejecutado_o_proyecta_2</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_correctivo_ejecutado_o_proyecta_3</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>monto_anual_de_mantenimiento_correctivo_ejecutado_o_proyecta_4</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>alcance_activos_intervenidos_equipamiento_educativo_mobiliar</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>avance</t>
+          <t>centro_poblado</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>ano_de_la_entrega_del_peip</t>
+          <t>ubigeo</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>fecha_de_inicio_del_mantenimiento_o_estimada</t>
+          <t>dre</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>fecha_de_culminacion_de_mantenimiento_o_estimada</t>
+          <t>ugel</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>area</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
-        <is>
-          <t>provincia</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>distrito</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>centro_poblado</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>ubigeo</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>dre</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>ugel</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>nombre_ie_2</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -613,102 +573,90 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>245014.47</v>
+      </c>
       <c r="H2" t="n">
-        <v>245014.47</v>
+        <v>61253.61750000001</v>
       </c>
       <c r="I2" t="n">
-        <v>245014.47</v>
+        <v>344058.55</v>
       </c>
       <c r="J2" t="n">
-        <v>61253.61750000001</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>172029.275</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>344058.55</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>344058.55</v>
-      </c>
-      <c r="N2" t="n">
-        <v>172029.275</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>11/06/2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2024</v>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>150117</t>
+        </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>LOS OLIVOS</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>LOS OLIVOS</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>150117</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>UGEL 02 RÍMAC</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -739,102 +687,90 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>365311.43</v>
+      </c>
       <c r="H3" t="n">
-        <v>365311.43</v>
+        <v>91327.8575</v>
       </c>
       <c r="I3" t="n">
-        <v>365311.43</v>
+        <v>469471.54</v>
       </c>
       <c r="J3" t="n">
-        <v>91327.8575</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>234735.77</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>469471.54</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>469471.54</v>
-      </c>
-      <c r="N3" t="n">
-        <v>234735.77</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>11/06/2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2024</v>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>LIMA CERCADO</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>150101</t>
+        </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 03 BREÑA</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>0035 NUESTRA SEÑORA DE LA VISITACION/0035 NUESTRA SEÑORA DE LA VISITACION/0035 NUESTRA SEÑORA DE LA VISITACION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>LIMA CERCADO</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>UGEL 03 BREÑA</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0035 NUESTRA SEÑORA DE LA VISITACION/0035 NUESTRA SEÑORA DE LA VISITACION/0035 NUESTRA SEÑORA DE LA VISITACION</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -865,102 +801,90 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>405598.37</v>
+      </c>
       <c r="H4" t="n">
-        <v>405598.37</v>
+        <v>101399.5925</v>
       </c>
       <c r="I4" t="n">
-        <v>405598.37</v>
+        <v>511471.81</v>
       </c>
       <c r="J4" t="n">
-        <v>101399.5925</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>255735.905</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>511471.81</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>511471.81</v>
-      </c>
-      <c r="N4" t="n">
-        <v>255735.905</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>11/06/2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2024</v>
+          <t>EL AGUSTINO</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>EL AGUSTINO</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>150111</t>
+        </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>EL AGUSTINO</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>EL AGUSTINO</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>150111</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -991,102 +915,90 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>438373.19</v>
+      </c>
       <c r="H5" t="n">
-        <v>438373.19</v>
+        <v>109593.2975</v>
       </c>
       <c r="I5" t="n">
-        <v>438373.19</v>
+        <v>634264.53</v>
       </c>
       <c r="J5" t="n">
-        <v>109593.2975</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>317132.265</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>634264.53</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>634264.53</v>
-      </c>
-      <c r="N5" t="n">
-        <v>317132.265</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>11/06/2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2024</v>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>COMAS</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>150110</t>
+        </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 04 COMAS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>SAN FELIPE/SAN FELIPE</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>COMAS</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>COMAS</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>150110</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>UGEL 04 COMAS</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>SAN FELIPE/SAN FELIPE</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -1117,102 +1029,90 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>443448.39</v>
+      </c>
       <c r="H6" t="n">
-        <v>443448.39</v>
+        <v>110862.0975</v>
       </c>
       <c r="I6" t="n">
-        <v>443448.39</v>
+        <v>516568.69</v>
       </c>
       <c r="J6" t="n">
-        <v>110862.0975</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>258284.345</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>516568.69</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>516568.69</v>
-      </c>
-      <c r="N6" t="n">
-        <v>258284.345</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+        <v>2025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2025</v>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>1268 GUSTAVO MOHME LLONA/1268 GUSTAVO MOHME LLONA</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>VITARTE</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>1268 GUSTAVO MOHME LLONA/1268 GUSTAVO MOHME LLONA</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -1243,102 +1143,90 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>386946.03</v>
+      </c>
       <c r="H7" t="n">
-        <v>386946.03</v>
+        <v>96736.50750000001</v>
       </c>
       <c r="I7" t="n">
-        <v>386946.03</v>
+        <v>620446.98</v>
       </c>
       <c r="J7" t="n">
-        <v>96736.50750000001</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>310223.49</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>620446.98</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>620446.98</v>
-      </c>
-      <c r="N7" t="n">
-        <v>310223.49</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+        <v>2025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2025</v>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>1209 MARISCAL TORIBIO DE LUZURIAGA/1209 MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>VITARTE</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>1209 MARISCAL TORIBIO DE LUZURIAGA/1209 MARISCAL TORIBIO DE LUZURIAGA</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -1369,102 +1257,90 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>925947.16</v>
+      </c>
       <c r="H8" t="n">
-        <v>925947.16</v>
+        <v>231486.79</v>
       </c>
       <c r="I8" t="n">
-        <v>925947.16</v>
+        <v>1453676.9</v>
       </c>
       <c r="J8" t="n">
-        <v>231486.79</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>726838.45</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>1453676.9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1453676.9</v>
-      </c>
-      <c r="N8" t="n">
-        <v>726838.45</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+        <v>2025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2025</v>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALEZ PRADA</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>VITARTE</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALEZ PRADA</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -1495,102 +1371,90 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>527451.5</v>
+      </c>
       <c r="H9" t="n">
-        <v>527451.5</v>
+        <v>131862.875</v>
       </c>
       <c r="I9" t="n">
-        <v>527451.5</v>
+        <v>929711.5</v>
       </c>
       <c r="J9" t="n">
-        <v>131862.875</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>464855.75</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>929711.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>929711.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>464855.75</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+        <v>2025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2025</v>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>VICTOR RAUL HAYA DE LA TORRE/046 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>VITARTE</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>VICTOR RAUL HAYA DE LA TORRE/046 VICTOR RAUL HAYA DE LA TORRE</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -1621,102 +1485,90 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>551198.48</v>
+      </c>
       <c r="H10" t="n">
-        <v>551198.48</v>
+        <v>137799.62</v>
       </c>
       <c r="I10" t="n">
-        <v>551198.48</v>
+        <v>683162.4</v>
       </c>
       <c r="J10" t="n">
-        <v>137799.62</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>341581.2</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>683162.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>683162.4</v>
-      </c>
-      <c r="N10" t="n">
-        <v>341581.2</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+        <v>2025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2025</v>
+          <t>LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>150118</t>
+        </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>1267/1267/1267</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>LURIGANCHO</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>LURIGANCHO</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>150118</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>1267/1267/1267</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -1747,102 +1599,90 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>486713.03</v>
+      </c>
       <c r="H11" t="n">
-        <v>486713.03</v>
+        <v>121678.2575</v>
       </c>
       <c r="I11" t="n">
-        <v>486713.03</v>
+        <v>561673.29</v>
       </c>
       <c r="J11" t="n">
-        <v>121678.2575</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>280836.645</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>561673.29</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>561673.29</v>
-      </c>
-      <c r="N11" t="n">
-        <v>280836.645</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+        <v>2025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2025</v>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>150117</t>
+        </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>3080 PERU - CANADA/3080 PERU - CANADA</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>LOS OLIVOS</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>LOS OLIVOS</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>150117</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>UGEL 02 RÍMAC</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>3080 PERU - CANADA/3080 PERU - CANADA</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -1873,102 +1713,90 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>626924.48</v>
+      </c>
       <c r="H12" t="n">
-        <v>626924.48</v>
+        <v>156731.12</v>
       </c>
       <c r="I12" t="n">
-        <v>626924.48</v>
+        <v>762108.89</v>
       </c>
       <c r="J12" t="n">
-        <v>156731.12</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>381054.445</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>762108.89</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>762108.89</v>
-      </c>
-      <c r="N12" t="n">
-        <v>381054.445</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+        <v>2025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2025</v>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>1255 WALTER PEÑALOZA RAMELLA/1255 WALTER PEÑALOZA RAMELLA</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>VITARTE</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>1255 WALTER PEÑALOZA RAMELLA/1255 WALTER PEÑALOZA RAMELLA</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -1999,102 +1827,90 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>181556.8</v>
+      </c>
       <c r="H13" t="n">
-        <v>181556.8</v>
+        <v>45389.2</v>
       </c>
       <c r="I13" t="n">
-        <v>181556.8</v>
+        <v>189278.1</v>
       </c>
       <c r="J13" t="n">
-        <v>45389.2</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>94639.05</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>189278.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>189278.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>94639.05</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+        <v>2025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2025</v>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>VITARTE</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>150103</t>
+        </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>0034 PERUANO FINLANDES</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>ATE</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>VITARTE</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>150103</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>0034 PERUANO FINLANDES</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -2125,102 +1941,90 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>483836.3</v>
+      </c>
       <c r="H14" t="n">
-        <v>483836.3</v>
+        <v>120959.075</v>
       </c>
       <c r="I14" t="n">
-        <v>483836.3</v>
+        <v>721457.8199999999</v>
       </c>
       <c r="J14" t="n">
-        <v>120959.075</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+        <v>360728.91</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>721457.8199999999</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>721457.8199999999</v>
-      </c>
-      <c r="N14" t="n">
-        <v>360728.91</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2024</v>
+          <t>LA MOLINA</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>LA MOLINA</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -2251,102 +2055,90 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>448674.75</v>
+      </c>
       <c r="H15" t="n">
-        <v>448674.75</v>
+        <v>112168.6875</v>
       </c>
       <c r="I15" t="n">
-        <v>448674.75</v>
+        <v>576278.51</v>
       </c>
       <c r="J15" t="n">
-        <v>112168.6875</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>288139.255</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>576278.51</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>576278.51</v>
-      </c>
-      <c r="N15" t="n">
-        <v>288139.255</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2024</v>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>CHORRILLOS</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>150108</t>
+        </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>6094 SANTA ROSA/6094 SANTA ROSA</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>CHORRILLOS</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>CHORRILLOS</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>150108</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>UGEL 07 SAN BORJA</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>6094 SANTA ROSA/6094 SANTA ROSA</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -2377,102 +2169,90 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>472631.57</v>
+      </c>
       <c r="H16" t="n">
-        <v>472631.57</v>
+        <v>118157.8925</v>
       </c>
       <c r="I16" t="n">
-        <v>472631.57</v>
+        <v>492731.78</v>
       </c>
       <c r="J16" t="n">
-        <v>118157.8925</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>246365.89</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>492731.78</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>492731.78</v>
-      </c>
-      <c r="N16" t="n">
-        <v>246365.89</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2024</v>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>150134</t>
+        </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>0083 SAN JUAN MACIAS/0083 SAN JUAN MACIAS</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>SAN LUIS</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>SAN LUIS</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>150134</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>UGEL 07 SAN BORJA</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>0083 SAN JUAN MACIAS/0083 SAN JUAN MACIAS</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -2503,102 +2283,90 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>369766.7</v>
+      </c>
       <c r="H17" t="n">
-        <v>369766.7</v>
+        <v>92441.675</v>
       </c>
       <c r="I17" t="n">
-        <v>369766.7</v>
+        <v>439753.44</v>
       </c>
       <c r="J17" t="n">
-        <v>92441.675</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+        <v>219876.72</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>439753.44</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>439753.44</v>
-      </c>
-      <c r="N17" t="n">
-        <v>219876.72</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2024</v>
+          <t>SANTA ANITA</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SANTA ANITA</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>150137</t>
+        </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 06 ATE</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>UGEL 06 ATE</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -2629,102 +2397,90 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>467638.29</v>
+      </c>
       <c r="H18" t="n">
-        <v>467638.29</v>
+        <v>116909.5725</v>
       </c>
       <c r="I18" t="n">
-        <v>467638.29</v>
+        <v>650309.74</v>
       </c>
       <c r="J18" t="n">
-        <v>116909.5725</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>325154.87</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>650309.74</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>650309.74</v>
-      </c>
-      <c r="N18" t="n">
-        <v>325154.87</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2024</v>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>150133</t>
+        </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>7207 MARISCAL RAMON CASTILLA/7207 MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>150133</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>7207 MARISCAL RAMON CASTILLA/7207 MARISCAL RAMON CASTILLA</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -2755,102 +2511,90 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>523736.69</v>
+      </c>
       <c r="H19" t="n">
-        <v>523736.69</v>
+        <v>130934.1725</v>
       </c>
       <c r="I19" t="n">
-        <v>523736.69</v>
+        <v>654532.71</v>
       </c>
       <c r="J19" t="n">
-        <v>130934.1725</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
+        <v>327266.355</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>654532.71</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>654532.71</v>
-      </c>
-      <c r="N19" t="n">
-        <v>327266.355</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2024</v>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>LOS PRECURSORES</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>150140</t>
+        </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>7086 LOS PRECURSORES/7086 LOS PRECURSORES/7086 LOS PRECURSORES</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>SANTIAGO DE SURCO</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>LOS PRECURSORES</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>150140</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>UGEL 07 SAN BORJA</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>7086 LOS PRECURSORES/7086 LOS PRECURSORES/7086 LOS PRECURSORES</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -2881,102 +2625,90 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>512259.31</v>
+      </c>
       <c r="H20" t="n">
-        <v>512259.31</v>
+        <v>128064.8275</v>
       </c>
       <c r="I20" t="n">
-        <v>512259.31</v>
+        <v>642567.21</v>
       </c>
       <c r="J20" t="n">
-        <v>128064.8275</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>321283.605</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L20" t="n">
-        <v>642567.21</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>642567.21</v>
-      </c>
-      <c r="N20" t="n">
-        <v>321283.605</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2024</v>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SANTIAGO DE SURCO</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>150140</t>
+        </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>6082 LOS PROCERES/6082 LOS PROCERES</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>SANTIAGO DE SURCO</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>SANTIAGO DE SURCO</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>150140</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>UGEL 07 SAN BORJA</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>6082 LOS PROCERES/6082 LOS PROCERES</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -3007,102 +2739,90 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>669200.89</v>
+      </c>
       <c r="H21" t="n">
-        <v>669200.89</v>
+        <v>167300.2225</v>
       </c>
       <c r="I21" t="n">
-        <v>669200.89</v>
+        <v>1131750.45</v>
       </c>
       <c r="J21" t="n">
-        <v>167300.2225</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>565875.225</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L21" t="n">
-        <v>1131750.45</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1131750.45</v>
-      </c>
-      <c r="N21" t="n">
-        <v>565875.225</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2024</v>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>150133</t>
+        </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>JAVIER HERAUD/JAVIER HERAUD</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>150133</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>JAVIER HERAUD/JAVIER HERAUD</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -3133,102 +2853,90 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>409693.48</v>
+      </c>
       <c r="H22" t="n">
-        <v>409693.48</v>
+        <v>102423.37</v>
       </c>
       <c r="I22" t="n">
-        <v>409693.48</v>
+        <v>427117.04</v>
       </c>
       <c r="J22" t="n">
-        <v>102423.37</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
+        <v>213558.52</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L22" t="n">
-        <v>427117.04</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>427117.04</v>
-      </c>
-      <c r="N22" t="n">
-        <v>213558.52</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2024</v>
+          <t>RIMAC</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>RIMAC</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>150128</t>
+        </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>2099 PATRICIA ROSA MERINO/2099 PATRICIA ROSA MERINO</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>RIMAC</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>RIMAC</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>150128</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>UGEL 02 RÍMAC</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>2099 PATRICIA ROSA MERINO/2099 PATRICIA ROSA MERINO</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -3259,102 +2967,90 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>353857.06</v>
+      </c>
       <c r="H23" t="n">
-        <v>353857.06</v>
+        <v>88464.265</v>
       </c>
       <c r="I23" t="n">
-        <v>353857.06</v>
+        <v>423167.19</v>
       </c>
       <c r="J23" t="n">
-        <v>88464.265</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
+        <v>211583.595</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L23" t="n">
-        <v>423167.19</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>423167.19</v>
-      </c>
-      <c r="N23" t="n">
-        <v>211583.595</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2024</v>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>LIMA CERCADO</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>150101</t>
+        </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 03 BREÑA</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>101 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>LIMA CERCADO</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>UGEL 03 BREÑA</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>101 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -3385,102 +3081,90 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>337397.07</v>
+      </c>
       <c r="H24" t="n">
-        <v>337397.07</v>
+        <v>84349.2675</v>
       </c>
       <c r="I24" t="n">
-        <v>337397.07</v>
+        <v>406007.18</v>
       </c>
       <c r="J24" t="n">
-        <v>84349.2675</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+        <v>203003.59</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NINGUNO</t>
+        </is>
+      </c>
       <c r="L24" t="n">
-        <v>406007.18</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>406007.18</v>
-      </c>
-      <c r="N24" t="n">
-        <v>203003.59</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>01/03/2028</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>No se cuenta con presupuesto asignado a la fecha</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>NINGUNO</t>
-        </is>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2024</v>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>LIMA CERCADO</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>150101</t>
+        </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>15/07/2025</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>01/03/2028</t>
+          <t>UGEL 03 BREÑA</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>No se cuenta con presupuesto asignado a la fecha</t>
+          <t>1124 JOSE MARTI/1124 JOSE MARTI</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>LIMA CERCADO</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>UGEL 03 BREÑA</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>1124 JOSE MARTI/1124 JOSE MARTI</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
